--- a/artfynd/A 40315-2025 artfynd.xlsx
+++ b/artfynd/A 40315-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134765583</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rodga, Lövdalen, 150 m norr vägskälet., Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>563741</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6513055</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Charlotte Wigermo, Åke Svensson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40315-2025 artfynd.xlsx
+++ b/artfynd/A 40315-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120146719</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134765583</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>